--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2173,9 +2173,777 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Connect &amp; authenticate</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>GML-1</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/GmailDownloader.cs (RunAsync)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>n/a (network - covered by QA + manual run)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Gmail_feature_resolves_its_own_private_MailKit)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L27" s="2">
+        <f>IF(COUNTA(D27,F27,G27,H27,I27,K27)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>App password + 2-Step Verification required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Folder/label traversal (read-only)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>GML-2, GML-3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/GmailDownloader.cs (CollectSelectableFoldersAsync)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>n/a (network - covered by QA + manual run)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L28" s="2">
+        <f>IF(COUNTA(D28,F28,G28,H28,I28,K28)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>EXAMINE / read-only; labels can overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Save .txt + .eml + mirror</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GML-4, GML-6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/GmailDownloader.cs (SaveMessage), src/Features/GmailDownloader/GmailFileNaming.cs</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/GmailFileNamingTests.cs</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L29" s="2">
+        <f>IF(COUNTA(D29,F29,G29,H29,I29,K29)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Attachments (incl. inline)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GML-5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/GmailAttachmentScanner.cs</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/GmailAttachmentScannerTests.cs</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L30" s="2">
+        <f>IF(COUNTA(D30,F30,G30,H30,I30,K30)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Progress &amp; cancel + errors</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GML-7</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/DownloadGmailControl.cs (OnStart, OnCancel)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L31" s="2">
+        <f>IF(COUNTA(D31,F31,G31,H31,I31,K31)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Download Gmail</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Settings (remember; no password)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GML-8</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/gmail-downloader.md</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/gmail-downloader.png</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/GmailSettings.cs (GmailSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StoreTests.cs (Gmail_settings_round_trip)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#gmail</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GmailDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L32" s="2">
+        <f>IF(COUNTA(D32,F32,G32,H32,I32,K32)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Password never stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>OAuth sign-in (read-only)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>GDR-1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/GoogleDriveDownloader.cs (CreateServiceAsync)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>n/a (network - covered by QA + manual run)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Drive_feature_resolves_its_own_private_Google_Apis)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L33" s="2">
+        <f>IF(COUNTA(D33,F33,G33,H33,I33,K33)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Desktop-app OAuth client; token cached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>List &amp; build folder tree</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GDR-2, GDR-3</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/GoogleDriveDownloader.cs (ListAllAsync), src/Features/GoogleDriveDownloader/DriveFileNaming.cs (ResolveFolderPath)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DriveFileNamingTests.cs</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L34" s="2">
+        <f>IF(COUNTA(D34,F34,G34,H34,I34,K34)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Download regular files</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>GDR-4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/GoogleDriveDownloader.cs (DownloadAsync)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>n/a (network - covered by QA + manual run)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L35" s="2">
+        <f>IF(COUNTA(D35,F35,G35,H35,I35,K35)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Saved byte-for-byte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Export Google docs (Office + PDF)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>GDR-5, GDR-6</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/GoogleExportFormats.cs, src/Features/GoogleDriveDownloader/GoogleDriveDownloader.cs (ExportAsync)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/GoogleExportFormatsTests.cs</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L36" s="2">
+        <f>IF(COUNTA(D36,F36,G36,H36,I36,K36)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Progress &amp; cancel + errors</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>GDR-7</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/DownloadDriveControl.cs (OnStart, OnCancel)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L37" s="2">
+        <f>IF(COUNTA(D37,F37,G37,H37,I37,K37)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Download Google Drive</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Settings (remember path; token cached)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>GDR-8</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/google-drive-downloader.md</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/google-drive-downloader.png</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/DriveSettings.cs (DriveSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StoreTests.cs (Drive_settings_round_trip_remembers_path_not_token)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#drive</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/GoogleDriveDownloader/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L38" s="2">
+        <f>IF(COUNTA(D38,F38,G38,H38,I38,K38)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Token cached separately, not in settings.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L26">
+  <conditionalFormatting sqref="L2:L38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2941,9 +2941,1301 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Ingest &amp; parse (.eml/.txt)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EI-A1, EI-A2, EI-A3, EI-A4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/EmailParser.cs (ParseEml, ParseTxt), src/Features/EmailIntelligence/ArchiveScanner.cs (Filter)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/EmailParserTests.cs, tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/ArchiveScannerTests.cs</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L39" s="2">
+        <f>IF(COUNTA(D39,F39,G39,H39,I39,K39)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>MimeKit + .txt; .eml preferred over .txt sibling; offline decoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Clean &amp; de-duplicate + threads</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EI-B1, EI-B2, EI-B3</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/Deduplicator.cs (KeyFor, ThreadKey)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/DeduplicatorTests.cs</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L40" s="2">
+        <f>IF(COUNTA(D40,F40,G40,H40,I40,K40)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Message-Id + content hash; thread key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Message classification</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EI-B4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/MessageClassifier.cs (Classify)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/MessageClassifierTests.cs</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L41" s="2">
+        <f>IF(COUNTA(D41,F41,G41,H41,I41,K41)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Contacts &amp; identity resolution</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EI-C1, EI-C2, EI-C3, EI-C4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/ContactExtractor.cs (DetectOwner), src/Features/EmailIntelligence/IdentityResolver.cs (Resolve)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IdentityResolverTests.cs</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L42" s="2">
+        <f>IF(COUNTA(D42,F42,G42,H42,I42,K42)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Merge addresses by full name; owner excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Signature detail extraction</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EI-C5</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/SignatureExtractor.cs (Extract)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/SignatureExtractorTests.cs</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L43" s="2">
+        <f>IF(COUNTA(D43,F43,G43,H43,I43,K43)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Contact export (vCard/CSV)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EI-C6</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/Exporters.cs (VCardExporter, CsvExporter)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/ExportersTests.cs</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L44" s="2">
+        <f>IF(COUNTA(D44,F44,G44,H44,I44,K44)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Relationship metrics &amp; strength</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EI-D1, EI-D2, EI-D3</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/RelationshipAnalyzer.cs (Analyze)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/RelationshipAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L45" s="2">
+        <f>IF(COUNTA(D45,F45,G45,H45,I45,K45)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Network graph &amp; organization</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EI-D4, EI-D5</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/NetworkGraphBuilder.cs (Build), src/Features/EmailIntelligence/IntelligencePipeline.cs (OrganizationFor)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/NetworkGraphBuilderTests.cs, tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L46" s="2">
+        <f>IF(COUNTA(D46,F46,G46,H46,I46,K46)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Topic extraction</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EI-E1</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/TopicExtractor.cs (GlobalTopics, AssignTopics)</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/TopicExtractorTests.cs</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L47" s="2">
+        <f>IF(COUNTA(D47,F47,G47,H47,I47,K47)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Tone &amp; sentiment (lexicon)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EI-E2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/ToneAnalyzer.cs (Analyze, ScoreText), src/Features/EmailIntelligence/SentimentLexicon.cs</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/ToneAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L48" s="2">
+        <f>IF(COUNTA(D48,F48,G48,H48,I48,K48)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Offline lexicon; heuristic, not AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Life-data extraction</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EI-F1, EI-F2, EI-F3, EI-F4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/LifeDataExtractor.cs (Extract, Categorize, FindAmount)</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/LifeDataExtractorTests.cs</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L49" s="2">
+        <f>IF(COUNTA(D49,F49,G49,H49,I49,K49)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Purchases / subscriptions / travel / accounts; heuristic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Useful-document library</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EI-F7</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/DocumentLibrary.cs (Build, Classify)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/DocumentLibraryTests.cs</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L50" s="2">
+        <f>IF(COUNTA(D50,F50,G50,H50,I50,K50)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Hash-deduped attachments, typed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Relationship-history timeline</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EI-G6</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/TimelineBuilder.cs (Build)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/TimelineBuilderTests.cs</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L51" s="2">
+        <f>IF(COUNTA(D51,F51,G51,H51,I51,K51)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Portable outputs (JSON/CSV/GraphML)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EI-H1, EI-H2, EI-H5</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/Exporters.cs (JsonExporter, GraphMlExporter)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/ExportersTests.cs</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L52" s="2">
+        <f>IF(COUNTA(D52,F52,G52,H52,I52,K52)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>No database; files only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Unified HTML5 report</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EI-K1, EI-K2, EI-K3, EI-K4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (Write)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/HtmlReportGeneratorTests.cs</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L53" s="2">
+        <f>IF(COUNTA(D53,F53,G53,H53,I53,K53)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Offline; tabs; data loaded via script tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>People search &amp; dossier</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EI-G1, EI-G2, EI-G4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (AppJs)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/HtmlReportGeneratorTests.cs</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L54" s="2">
+        <f>IF(COUNTA(D54,F54,G54,H54,I54,K54)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Search, dossier, drill-through to source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline orchestration &amp; progress</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EI-J5, EI-I1</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (Analyze, RunAndExport)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L55" s="2">
+        <f>IF(COUNTA(D55,F55,G55,H55,I55,K55)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Phased progress; idempotent re-run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Append &amp; consolidate archives</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EI-I4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (RunAndExport, ScanAndParse, AnalyzeCore), src/Features/EmailIntelligence/MessageStore.cs (Save, Load)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/MessageStoreTests.cs, tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L56" s="2">
+        <f>IF(COUNTA(D56,F56,G56,H56,I56,K56)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Persist deduped corpus; append merges + re-dedupes across archives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Settings (folders; no secrets)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EI-J1, EI-J3</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/EmailIntelligenceSettings.cs (EmailIntelligenceSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/EmailIntelligenceSettingsTests.cs</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L57" s="2">
+        <f>IF(COUNTA(D57,F57,G57,H57,I57,K57)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>No secrets stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>UI (progress/cancel/open report)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EI-J2, EI-J4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/EmailIntelligenceControl.cs (OnStart, OnCancel, OnProgress)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L58" s="2">
+        <f>IF(COUNTA(D58,F58,G58,H58,I58,K58)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>UI wires logic; covered by QA automation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L38">
+  <conditionalFormatting sqref="L2:L58">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Unified HTML5 report</t>
+          <t>Native Excel workbook (.xlsx)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EI-K1, EI-K2, EI-K3, EI-K4</t>
+          <t>EI-H7</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (Write)</t>
+          <t>src/Features/EmailIntelligence/XlsxWriter.cs (Write, ColumnName), src/Features/EmailIntelligence/Exporters.cs (WorkbookExporter)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/HtmlReportGeneratorTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/XlsxWriterTests.cs</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Offline; tabs; data loaded via script tag.</t>
+          <t>Dependency-free OOXML writer; multi-sheet; typed numeric cells.</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>People search &amp; dossier</t>
+          <t>Unified HTML5 report</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EI-G1, EI-G2, EI-G4</t>
+          <t>EI-K1, EI-K2, EI-K3, EI-K4</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (AppJs)</t>
+          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (Write)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Search, dossier, drill-through to source.</t>
+          <t>Offline; tabs; data loaded via script tag.</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Pipeline orchestration &amp; progress</t>
+          <t>People search &amp; dossier</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EI-J5, EI-I1</t>
+          <t>EI-G1, EI-G2, EI-G4</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (Analyze, RunAndExport)</t>
+          <t>src/Features/EmailIntelligence/HtmlReportGenerator.cs (AppJs)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/HtmlReportGeneratorTests.cs</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Phased progress; idempotent re-run.</t>
+          <t>Search, dossier, drill-through to source.</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4043,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Append &amp; consolidate archives</t>
+          <t>Pipeline orchestration &amp; progress</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EI-I4</t>
+          <t>EI-J5, EI-I1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (RunAndExport, ScanAndParse, AnalyzeCore), src/Features/EmailIntelligence/MessageStore.cs (Save, Load)</t>
+          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (Analyze, RunAndExport)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/MessageStoreTests.cs, tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Persist deduped corpus; append merges + re-dedupes across archives.</t>
+          <t>Phased progress; idempotent re-run.</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Settings (folders; no secrets)</t>
+          <t>Append &amp; consolidate archives</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EI-J1, EI-J3</t>
+          <t>EI-I4</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/EmailIntelligenceSettings.cs (EmailIntelligenceSettingsStore)</t>
+          <t>src/Features/EmailIntelligence/IntelligencePipeline.cs (RunAndExport, ScanAndParse, AnalyzeCore), src/Features/EmailIntelligence/MessageStore.cs (Save, Load)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/EmailIntelligenceSettingsTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/MessageStoreTests.cs, tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/IntelligencePipelineTests.cs</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>No secrets stored.</t>
+          <t>Persist deduped corpus; append merges + re-dedupes across archives.</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>UI (progress/cancel/open report)</t>
+          <t>Settings (folders; no secrets)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EI-J2, EI-J4</t>
+          <t>EI-J1, EI-J3</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>src/Features/EmailIntelligence/EmailIntelligenceControl.cs (OnStart, OnCancel, OnProgress)</t>
+          <t>src/Features/EmailIntelligence/EmailIntelligenceSettings.cs (EmailIntelligenceSettingsStore)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>n/a (UI - covered by QA automation)</t>
+          <t>tests/DigitalSecretary.UnitTests/Features/EmailIntelligence/EmailIntelligenceSettingsTests.cs</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4229,13 +4229,79 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
+          <t>No secrets stored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Email Intelligence</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>UI (progress/cancel/open report)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EI-J2, EI-J4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/EmailIntelligenceControl.cs (OnStart, OnCancel, OnProgress)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/features/email-intelligence.md</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/EmailIntelligence/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L59" s="2">
+        <f>IF(COUNTA(D59,F59,G59,H59,I59,K59)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>UI wires logic; covered by QA automation.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L58">
+  <conditionalFormatting sqref="L2:L59">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>
